--- a/public/download/create_user.xlsx
+++ b/public/download/create_user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\win-paloteo\public\download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6156B2AB-C48E-46BA-B67E-C800ABF5A68B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2932FCE-F509-4304-93F5-B7B487F9E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22620" windowHeight="13500" xr2:uid="{B58EF809-3A37-4D7C-BF5B-804219BF9F00}"/>
+    <workbookView xWindow="-4260" yWindow="-14190" windowWidth="16800" windowHeight="9675" xr2:uid="{B58EF809-3A37-4D7C-BF5B-804219BF9F00}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
   <si>
     <t>tdoc</t>
   </si>
@@ -64,9 +64,6 @@
     <t>12345678</t>
   </si>
   <si>
-    <t>1234567</t>
-  </si>
-  <si>
     <t>AP PATERNO</t>
   </si>
   <si>
@@ -74,6 +71,12 @@
   </si>
   <si>
     <t>NOMBRES</t>
+  </si>
+  <si>
+    <t>12345670</t>
+  </si>
+  <si>
+    <t>xd</t>
   </si>
 </sst>
 </file>
@@ -137,15 +140,13 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="49" fontId="2" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -496,13 +497,13 @@
         <v>10</v>
       </c>
       <c r="C2" t="s">
+        <v>11</v>
+      </c>
+      <c r="D2" t="s">
         <v>12</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
         <v>13</v>
-      </c>
-      <c r="E2" s="6" t="s">
-        <v>14</v>
       </c>
       <c r="F2" t="s">
         <v>9</v>
@@ -512,20 +513,20 @@
       <c r="A3" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="C3" t="s">
         <v>11</v>
       </c>
-      <c r="C3" t="s">
+      <c r="D3" t="s">
         <v>12</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
         <v>13</v>
       </c>
-      <c r="E3" s="6" t="s">
-        <v>14</v>
-      </c>
       <c r="F3" t="s">
-        <v>9</v>
+        <v>15</v>
       </c>
     </row>
   </sheetData>

--- a/public/download/create_user.xlsx
+++ b/public/download/create_user.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\xampp\htdocs\win-paloteo\public\download\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2932FCE-F509-4304-93F5-B7B487F9E16C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9DE1ABBB-DCB9-416E-A041-BBA87891A448}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-4260" yWindow="-14190" windowWidth="16800" windowHeight="9675" xr2:uid="{B58EF809-3A37-4D7C-BF5B-804219BF9F00}"/>
+    <workbookView xWindow="180" yWindow="-12120" windowWidth="16800" windowHeight="9675" xr2:uid="{B58EF809-3A37-4D7C-BF5B-804219BF9F00}"/>
   </bookViews>
   <sheets>
     <sheet name="data" sheetId="1" r:id="rId1"/>
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="14">
   <si>
     <t>tdoc</t>
   </si>
@@ -71,12 +71,6 @@
   </si>
   <si>
     <t>NOMBRES</t>
-  </si>
-  <si>
-    <t>12345670</t>
-  </si>
-  <si>
-    <t>xd</t>
   </si>
 </sst>
 </file>
@@ -461,7 +455,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8FE747DF-314A-4CDE-B50B-17A21F21DFF9}">
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F2"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="8.1796875" style="1" customWidth="1"/>
@@ -507,26 +501,6 @@
       </c>
       <c r="F2" t="s">
         <v>9</v>
-      </c>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.35">
-      <c r="A3" s="1" t="s">
-        <v>6</v>
-      </c>
-      <c r="B3" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="C3" t="s">
-        <v>11</v>
-      </c>
-      <c r="D3" t="s">
-        <v>12</v>
-      </c>
-      <c r="E3" t="s">
-        <v>13</v>
-      </c>
-      <c r="F3" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
